--- a/resources/templates/standard/K2100-08.xlsx
+++ b/resources/templates/standard/K2100-08.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="32">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>생산수량 대비 소모품 월소요량 및 안전재고</t>
   </si>
@@ -720,11 +723,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.1" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -754,14 +759,14 @@
       <c r="AD1" s="2"/>
       <c r="AE1" s="2"/>
       <c r="AF1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH1" s="4"/>
       <c r="AI1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ1" s="4"/>
     </row>
@@ -843,19 +848,19 @@
     </row>
     <row r="4" ht="16.5" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
@@ -877,7 +882,7 @@
       <c r="AA4" s="7"/>
       <c r="AB4" s="7"/>
       <c r="AC4" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD4" s="8"/>
       <c r="AE4" s="8"/>
@@ -955,23 +960,23 @@
       <c r="AA6" s="9"/>
       <c r="AB6" s="9"/>
       <c r="AC6" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD6" s="10"/>
       <c r="AE6" s="10"/>
       <c r="AF6" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG6" s="10"/>
       <c r="AH6" s="10"/>
       <c r="AI6" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ6" s="10"/>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -1001,7 +1006,7 @@
       <c r="AA7" s="12"/>
       <c r="AB7" s="12"/>
       <c r="AC7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD7" s="5"/>
       <c r="AE7" s="5"/>
@@ -1041,7 +1046,7 @@
       <c r="AA8" s="12"/>
       <c r="AB8" s="12"/>
       <c r="AC8" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD8" s="5"/>
       <c r="AE8" s="5"/>
@@ -1081,7 +1086,7 @@
       <c r="AA9" s="12"/>
       <c r="AB9" s="12"/>
       <c r="AC9" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD9" s="5"/>
       <c r="AE9" s="5"/>
@@ -1121,7 +1126,7 @@
       <c r="AA10" s="12"/>
       <c r="AB10" s="12"/>
       <c r="AC10" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD10" s="5"/>
       <c r="AE10" s="5"/>
@@ -1133,7 +1138,7 @@
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -1163,7 +1168,7 @@
       <c r="AA11" s="12"/>
       <c r="AB11" s="12"/>
       <c r="AC11" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD11" s="5"/>
       <c r="AE11" s="5"/>
@@ -1203,7 +1208,7 @@
       <c r="AA12" s="12"/>
       <c r="AB12" s="12"/>
       <c r="AC12" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD12" s="5"/>
       <c r="AE12" s="5"/>
@@ -1243,7 +1248,7 @@
       <c r="AA13" s="12"/>
       <c r="AB13" s="12"/>
       <c r="AC13" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD13" s="5"/>
       <c r="AE13" s="5"/>
@@ -1283,7 +1288,7 @@
       <c r="AA14" s="12"/>
       <c r="AB14" s="12"/>
       <c r="AC14" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD14" s="5"/>
       <c r="AE14" s="5"/>
@@ -1295,7 +1300,7 @@
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -1325,7 +1330,7 @@
       <c r="AA15" s="12"/>
       <c r="AB15" s="12"/>
       <c r="AC15" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD15" s="5"/>
       <c r="AE15" s="5"/>
@@ -1365,7 +1370,7 @@
       <c r="AA16" s="12"/>
       <c r="AB16" s="12"/>
       <c r="AC16" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD16" s="5"/>
       <c r="AE16" s="5"/>
@@ -1405,7 +1410,7 @@
       <c r="AA17" s="12"/>
       <c r="AB17" s="12"/>
       <c r="AC17" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD17" s="5"/>
       <c r="AE17" s="5"/>
@@ -1445,7 +1450,7 @@
       <c r="AA18" s="12"/>
       <c r="AB18" s="12"/>
       <c r="AC18" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD18" s="5"/>
       <c r="AE18" s="5"/>
@@ -1457,7 +1462,7 @@
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -1487,7 +1492,7 @@
       <c r="AA19" s="12"/>
       <c r="AB19" s="12"/>
       <c r="AC19" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD19" s="5"/>
       <c r="AE19" s="5"/>
@@ -1527,7 +1532,7 @@
       <c r="AA20" s="12"/>
       <c r="AB20" s="12"/>
       <c r="AC20" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD20" s="5"/>
       <c r="AE20" s="5"/>
@@ -1567,7 +1572,7 @@
       <c r="AA21" s="12"/>
       <c r="AB21" s="12"/>
       <c r="AC21" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD21" s="5"/>
       <c r="AE21" s="5"/>
@@ -1607,7 +1612,7 @@
       <c r="AA22" s="12"/>
       <c r="AB22" s="12"/>
       <c r="AC22" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD22" s="5"/>
       <c r="AE22" s="5"/>
@@ -1619,7 +1624,7 @@
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -1649,7 +1654,7 @@
       <c r="AA23" s="12"/>
       <c r="AB23" s="12"/>
       <c r="AC23" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD23" s="5"/>
       <c r="AE23" s="5"/>
@@ -1689,7 +1694,7 @@
       <c r="AA24" s="12"/>
       <c r="AB24" s="12"/>
       <c r="AC24" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD24" s="5"/>
       <c r="AE24" s="5"/>
@@ -1729,7 +1734,7 @@
       <c r="AA25" s="12"/>
       <c r="AB25" s="12"/>
       <c r="AC25" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD25" s="5"/>
       <c r="AE25" s="5"/>
@@ -1769,7 +1774,7 @@
       <c r="AA26" s="12"/>
       <c r="AB26" s="12"/>
       <c r="AC26" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD26" s="5"/>
       <c r="AE26" s="5"/>
@@ -1781,7 +1786,7 @@
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -1811,7 +1816,7 @@
       <c r="AA27" s="12"/>
       <c r="AB27" s="12"/>
       <c r="AC27" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD27" s="5"/>
       <c r="AE27" s="5"/>
@@ -1851,7 +1856,7 @@
       <c r="AA28" s="12"/>
       <c r="AB28" s="12"/>
       <c r="AC28" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD28" s="5"/>
       <c r="AE28" s="5"/>
@@ -1891,7 +1896,7 @@
       <c r="AA29" s="12"/>
       <c r="AB29" s="12"/>
       <c r="AC29" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD29" s="5"/>
       <c r="AE29" s="5"/>
@@ -1931,7 +1936,7 @@
       <c r="AA30" s="12"/>
       <c r="AB30" s="12"/>
       <c r="AC30" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD30" s="5"/>
       <c r="AE30" s="5"/>
@@ -1943,7 +1948,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -1973,7 +1978,7 @@
       <c r="AA31" s="12"/>
       <c r="AB31" s="12"/>
       <c r="AC31" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD31" s="5"/>
       <c r="AE31" s="5"/>
@@ -2013,7 +2018,7 @@
       <c r="AA32" s="12"/>
       <c r="AB32" s="12"/>
       <c r="AC32" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD32" s="5"/>
       <c r="AE32" s="5"/>
@@ -2053,7 +2058,7 @@
       <c r="AA33" s="12"/>
       <c r="AB33" s="12"/>
       <c r="AC33" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD33" s="5"/>
       <c r="AE33" s="5"/>
@@ -2093,7 +2098,7 @@
       <c r="AA34" s="12"/>
       <c r="AB34" s="12"/>
       <c r="AC34" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD34" s="5"/>
       <c r="AE34" s="5"/>
@@ -2105,7 +2110,7 @@
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -2135,7 +2140,7 @@
       <c r="AA35" s="12"/>
       <c r="AB35" s="12"/>
       <c r="AC35" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD35" s="5"/>
       <c r="AE35" s="5"/>
@@ -2175,7 +2180,7 @@
       <c r="AA36" s="12"/>
       <c r="AB36" s="12"/>
       <c r="AC36" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD36" s="5"/>
       <c r="AE36" s="5"/>
@@ -2215,7 +2220,7 @@
       <c r="AA37" s="12"/>
       <c r="AB37" s="12"/>
       <c r="AC37" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD37" s="5"/>
       <c r="AE37" s="5"/>
@@ -2255,7 +2260,7 @@
       <c r="AA38" s="12"/>
       <c r="AB38" s="12"/>
       <c r="AC38" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD38" s="5"/>
       <c r="AE38" s="5"/>
@@ -2267,7 +2272,7 @@
     </row>
     <row r="39" ht="18" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -2297,7 +2302,7 @@
       <c r="AA39" s="12"/>
       <c r="AB39" s="12"/>
       <c r="AC39" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD39" s="5"/>
       <c r="AE39" s="5"/>
@@ -2337,7 +2342,7 @@
       <c r="AA40" s="12"/>
       <c r="AB40" s="12"/>
       <c r="AC40" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD40" s="5"/>
       <c r="AE40" s="5"/>
@@ -2377,7 +2382,7 @@
       <c r="AA41" s="12"/>
       <c r="AB41" s="12"/>
       <c r="AC41" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD41" s="5"/>
       <c r="AE41" s="5"/>
@@ -2417,7 +2422,7 @@
       <c r="AA42" s="12"/>
       <c r="AB42" s="12"/>
       <c r="AC42" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD42" s="5"/>
       <c r="AE42" s="5"/>
@@ -2429,7 +2434,7 @@
     </row>
     <row r="43" ht="18" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B43" s="11"/>
       <c r="C43" s="11"/>
@@ -2459,7 +2464,7 @@
       <c r="AA43" s="12"/>
       <c r="AB43" s="12"/>
       <c r="AC43" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD43" s="5"/>
       <c r="AE43" s="5"/>
@@ -2499,7 +2504,7 @@
       <c r="AA44" s="12"/>
       <c r="AB44" s="12"/>
       <c r="AC44" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD44" s="5"/>
       <c r="AE44" s="5"/>
@@ -2539,7 +2544,7 @@
       <c r="AA45" s="12"/>
       <c r="AB45" s="12"/>
       <c r="AC45" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD45" s="5"/>
       <c r="AE45" s="5"/>
@@ -2579,7 +2584,7 @@
       <c r="AA46" s="12"/>
       <c r="AB46" s="12"/>
       <c r="AC46" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD46" s="5"/>
       <c r="AE46" s="5"/>
@@ -2591,7 +2596,7 @@
     </row>
     <row r="47" ht="18" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
@@ -2621,7 +2626,7 @@
       <c r="AA47" s="12"/>
       <c r="AB47" s="12"/>
       <c r="AC47" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD47" s="5"/>
       <c r="AE47" s="5"/>
@@ -2661,7 +2666,7 @@
       <c r="AA48" s="12"/>
       <c r="AB48" s="12"/>
       <c r="AC48" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD48" s="5"/>
       <c r="AE48" s="5"/>
@@ -2701,7 +2706,7 @@
       <c r="AA49" s="12"/>
       <c r="AB49" s="12"/>
       <c r="AC49" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD49" s="5"/>
       <c r="AE49" s="5"/>
@@ -2741,7 +2746,7 @@
       <c r="AA50" s="12"/>
       <c r="AB50" s="12"/>
       <c r="AC50" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD50" s="5"/>
       <c r="AE50" s="5"/>
@@ -2753,7 +2758,7 @@
     </row>
     <row r="51" ht="18" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
@@ -2783,7 +2788,7 @@
       <c r="AA51" s="12"/>
       <c r="AB51" s="12"/>
       <c r="AC51" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD51" s="5"/>
       <c r="AE51" s="5"/>
@@ -2823,7 +2828,7 @@
       <c r="AA52" s="12"/>
       <c r="AB52" s="12"/>
       <c r="AC52" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD52" s="5"/>
       <c r="AE52" s="5"/>
@@ -2863,7 +2868,7 @@
       <c r="AA53" s="12"/>
       <c r="AB53" s="12"/>
       <c r="AC53" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD53" s="5"/>
       <c r="AE53" s="5"/>
@@ -2903,7 +2908,7 @@
       <c r="AA54" s="12"/>
       <c r="AB54" s="12"/>
       <c r="AC54" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD54" s="14"/>
       <c r="AE54" s="14"/>
@@ -2915,7 +2920,7 @@
     </row>
     <row r="55" ht="24.95" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -2963,7 +2968,7 @@
     </row>
     <row r="56" ht="24.95" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
@@ -3015,13 +3020,13 @@
     </row>
     <row r="57" ht="24.95" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" s="21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
       <c r="E57" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F57" s="22"/>
       <c r="G57" s="22"/>
@@ -3073,7 +3078,7 @@
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
       <c r="E58" s="25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F58" s="25"/>
       <c r="G58" s="25"/>
